--- a/4.1.1 геометрическая оптика/измерения.xlsx
+++ b/4.1.1 геометрическая оптика/измерения.xlsx
@@ -9,15 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" firstSheet="3" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="оценка фокусов линз" sheetId="1" r:id="rId1"/>
     <sheet name="1определение фокусных расстояни" sheetId="2" r:id="rId2"/>
-    <sheet name="2 два  (2) (two) бессель " sheetId="3" r:id="rId3"/>
-    <sheet name="4 телескоп галлилея" sheetId="4" r:id="rId4"/>
-    <sheet name="5 микроскоп" sheetId="5" r:id="rId5"/>
-    <sheet name="6 измерение составной системы" sheetId="9" r:id="rId6"/>
+    <sheet name="1 вариант 2" sheetId="10" r:id="rId3"/>
+    <sheet name="2 два  (2) (two) бессель " sheetId="3" r:id="rId4"/>
+    <sheet name="4 телескоп галлилея" sheetId="4" r:id="rId5"/>
+    <sheet name="5 микроскоп" sheetId="5" r:id="rId6"/>
+    <sheet name="6 измерение составной системы" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,14 +30,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="71">
   <si>
     <t>номер линзы</t>
   </si>
   <si>
-    <t>f, см</t>
-  </si>
-  <si>
     <t>2.5</t>
   </si>
   <si>
@@ -64,9 +62,6 @@
     <t>юзаем лигзу 2.4 в положении типа 1</t>
   </si>
   <si>
-    <t>ВСЕ В МИЛЛИМЕТРАХ</t>
-  </si>
-  <si>
     <t>f1, mm</t>
   </si>
   <si>
@@ -161,6 +156,93 @@
   </si>
   <si>
     <t>НИЧЕГО НЕ ВЫШЛО</t>
+  </si>
+  <si>
+    <t>f_\sim, см</t>
+  </si>
+  <si>
+    <t>f_t_1, см</t>
+  </si>
+  <si>
+    <t>f_t_2, см</t>
+  </si>
+  <si>
+    <t>тут результаты телескопа</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>f2</t>
+  </si>
+  <si>
+    <t>собирающие</t>
+  </si>
+  <si>
+    <t>рассеивающие</t>
+  </si>
+  <si>
+    <t>D, см</t>
+  </si>
+  <si>
+    <t>d, см</t>
+  </si>
+  <si>
+    <t>погрешность</t>
+  </si>
+  <si>
+    <t>L = 86,9 см</t>
+  </si>
+  <si>
+    <t>delta_L = 0,2</t>
+  </si>
+  <si>
+    <t>delta_x = 0,1</t>
+  </si>
+  <si>
+    <t>L = 111,5</t>
+  </si>
+  <si>
+    <t>delta_L = 0,3</t>
+  </si>
+  <si>
+    <t>delta_x = 0,2</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>f_b, см</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>17,39 +- 0,08</t>
+  </si>
+  <si>
+    <t>7,9 +- 0,2</t>
+  </si>
+  <si>
+    <t>-9,2 +- 0,4</t>
+  </si>
+  <si>
+    <t>пересчет в расстояния до плоской стороны линзы</t>
+  </si>
+  <si>
+    <t>со стороны плоскости</t>
+  </si>
+  <si>
+    <t>со стороны кривизны</t>
+  </si>
+  <si>
+    <t>f, мм</t>
+  </si>
+  <si>
+    <t>df, мм</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
@@ -206,10 +288,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -490,69 +576,171 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="12.26953125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>7.1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B3">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>12.3</v>
+      </c>
+      <c r="D3">
+        <v>12.4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4">
+        <v>18</v>
+      </c>
+      <c r="C4">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D4">
+        <v>17.2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="C5">
+        <v>24.8</v>
+      </c>
+      <c r="D5">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>-14</v>
+      </c>
+      <c r="C6">
+        <v>-9.5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="B5">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
+      <c r="C7">
+        <v>4.8</v>
+      </c>
+      <c r="D7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>1.3</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:D7">
+    <sortCondition ref="A2:A7"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
@@ -560,7 +748,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.54296875" customWidth="1"/>
@@ -572,18 +760,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>48</v>
@@ -592,26 +780,26 @@
         <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
         <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>248</v>
@@ -631,7 +819,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>176</v>
@@ -639,10 +827,16 @@
       <c r="C5">
         <v>172</v>
       </c>
+      <c r="H5" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>123</v>
@@ -651,12 +845,20 @@
         <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="H6">
+        <f>H4-G4</f>
+        <v>-95</v>
+      </c>
+      <c r="I6">
+        <f>I4-G4</f>
+        <v>-92</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7">
         <v>71</v>
@@ -665,9 +867,97 @@
         <v>79</v>
       </c>
     </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
     <row r="10" spans="1:9" ht="33.5" x14ac:dyDescent="0.75">
-      <c r="F10" s="2" t="s">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <v>41</v>
+      </c>
+      <c r="C11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <f>-92 + 7</f>
+        <v>-85</v>
+      </c>
+      <c r="C12">
+        <f>-95 -7</f>
+        <v>-102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>241</v>
+      </c>
+      <c r="C13">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>169</v>
+      </c>
+      <c r="C14">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>116</v>
+      </c>
+      <c r="C15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>64</v>
+      </c>
+      <c r="C16">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -678,41 +968,196 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>64</v>
+      </c>
+      <c r="D2" s="4">
+        <f>((2 - $F$2) *C2 + B2)/(3 - $F$2)</f>
+        <v>78.666666666666671</v>
+      </c>
+      <c r="E2">
+        <f>((2 - $F$2) *2 + 2)/(3 - $F$2)</f>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>131</v>
+      </c>
+      <c r="C3">
+        <v>116</v>
+      </c>
+      <c r="D3" s="4">
+        <f>((2 - $F$2) *C3 + B3)/(3 - $F$2)</f>
+        <v>126</v>
+      </c>
+      <c r="E3">
+        <f>((2 - $F$2) *2 + 2)/(3 - $F$2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>179</v>
+      </c>
+      <c r="C4">
+        <v>169</v>
+      </c>
+      <c r="D4" s="4">
+        <f>((2 - $F$2) *C4 + B4)/(3 - $F$2)</f>
+        <v>175.66666666666666</v>
+      </c>
+      <c r="E4">
+        <f>((2 - $F$2) *2 + 2)/(3 - $F$2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>254</v>
+      </c>
+      <c r="C5">
+        <v>241</v>
+      </c>
+      <c r="D5" s="4">
+        <f>((2 - $F$2) *C5 + B5)/(3 - $F$2)</f>
+        <v>249.66666666666666</v>
+      </c>
+      <c r="E5">
+        <f>((2 - $F$2) *2 + 2)/(3 - $F$2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <f>-95 -7</f>
+        <v>-102</v>
+      </c>
+      <c r="C6">
+        <f>-92 + 7</f>
+        <v>-85</v>
+      </c>
+      <c r="D6" s="4">
+        <f>((2 - $F$2) *C6 + B6)/(3 - $F$2)</f>
+        <v>-96.333333333333329</v>
+      </c>
+      <c r="E6">
+        <f>((2 - $F$2) *4 + 4)/(3 - $F$2)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>41</v>
+      </c>
+      <c r="D7" s="4">
+        <f>((2 - $F$2) *C7 + B7)/(3 - $F$2)</f>
+        <v>54.333333333333336</v>
+      </c>
+      <c r="E7">
+        <f>((2 - $F$2) *2 + 2)/(3 - $F$2)</f>
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:E7">
+    <sortCondition ref="A2:A7"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
       <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -741,6 +1186,164 @@
       </c>
       <c r="I3">
         <v>799</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>239</v>
+      </c>
+      <c r="B7">
+        <v>1153</v>
+      </c>
+      <c r="C7">
+        <v>628</v>
+      </c>
+      <c r="D7">
+        <v>764</v>
+      </c>
+      <c r="F7">
+        <v>241</v>
+      </c>
+      <c r="G7">
+        <v>1148</v>
+      </c>
+      <c r="H7">
+        <v>628</v>
+      </c>
+      <c r="I7">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <f>B7-D7</f>
+        <v>389</v>
+      </c>
+      <c r="G8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8">
+        <f>G7-I7</f>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>215</v>
+      </c>
+      <c r="B12">
+        <v>1176</v>
+      </c>
+      <c r="C12">
+        <v>900</v>
+      </c>
+      <c r="D12">
+        <v>494</v>
+      </c>
+      <c r="F12">
+        <v>218</v>
+      </c>
+      <c r="G12">
+        <v>1175</v>
+      </c>
+      <c r="H12">
+        <v>904</v>
+      </c>
+      <c r="I12">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13">
+        <f>B12-D12</f>
+        <v>682</v>
+      </c>
+      <c r="G13" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13">
+        <f>G12-I12</f>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -748,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -760,35 +1363,35 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
         <v>23</v>
-      </c>
-      <c r="B1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -796,30 +1399,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -832,10 +1435,11 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -845,35 +1449,35 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
       <c r="F1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2">
         <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="I3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
@@ -900,7 +1504,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
